--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129909308</v>
+        <v>137284722</v>
       </c>
       <c r="B11" t="n">
-        <v>111175</v>
+        <v>9418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,37 +1649,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219677</v>
+        <v>101246</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Knösö, Bl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541609</v>
+        <v>541254</v>
       </c>
       <c r="R11" t="n">
-        <v>6225184</v>
+        <v>6225205</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,12 +1707,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Levande hane</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,24 +1742,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Via Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129909308</t>
+          <t>https://artportalen.se/Sighting/137284722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129909309</v>
+        <v>129909308</v>
       </c>
       <c r="B12" t="n">
         <v>111175</v>
@@ -1775,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541705</v>
+        <v>541609</v>
       </c>
       <c r="R12" t="n">
-        <v>6225086</v>
+        <v>6225184</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,13 +1855,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129909309</t>
+          <t>https://artportalen.se/Sighting/129909308</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129909310</v>
+        <v>129909309</v>
       </c>
       <c r="B13" t="n">
         <v>111175</v>
@@ -1877,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541322</v>
+        <v>541705</v>
       </c>
       <c r="R13" t="n">
-        <v>6225055</v>
+        <v>6225086</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1937,6 +1956,108 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129909309</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129909310</v>
+      </c>
+      <c r="B14" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Knösö, Bl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>541322</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6225055</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lösen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129909310</t>
         </is>
@@ -1956,6 +2077,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45735-2025 artfynd.xlsx
+++ b/artfynd/A 45735-2025 artfynd.xlsx
@@ -1641,7 +1641,7 @@
         <v>137284722</v>
       </c>
       <c r="B11" t="n">
-        <v>9418</v>
+        <v>9424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
